--- a/artfynd/A 26341-2025 artfynd.xlsx
+++ b/artfynd/A 26341-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129621965</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26341-2025 artfynd.xlsx
+++ b/artfynd/A 26341-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129621965</v>
       </c>
       <c r="B2" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,6 +804,133 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129723060</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57895</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Paljacka, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>604592</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6979054</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26341-2025 artfynd.xlsx
+++ b/artfynd/A 26341-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129621965</v>
       </c>
       <c r="B2" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>129723060</v>
       </c>
       <c r="B3" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26341-2025 artfynd.xlsx
+++ b/artfynd/A 26341-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -932,6 +932,520 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129910129</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57840</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Paljacka, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>604663</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6978951</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Flög runt mig en liten stund inne i skogen. Strulade med inspelning på telefonen därav dålig bild.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129917445</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Paljacka, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>604740</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6978947</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Sannolikt samma individ som i obsen strax innan.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129917306</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Paljacka, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>604679</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6978814</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129917397</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Paljacka, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>604719</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6978840</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26341-2025 artfynd.xlsx
+++ b/artfynd/A 26341-2025 artfynd.xlsx
@@ -937,7 +937,7 @@
         <v>129910129</v>
       </c>
       <c r="B4" t="n">
-        <v>57840</v>
+        <v>57841</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>129917445</v>
       </c>
       <c r="B5" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>129917306</v>
       </c>
       <c r="B6" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>129917397</v>
       </c>
       <c r="B7" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 26341-2025 artfynd.xlsx
+++ b/artfynd/A 26341-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129621965</v>
       </c>
       <c r="B2" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>129723060</v>
       </c>
       <c r="B3" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26341-2025 artfynd.xlsx
+++ b/artfynd/A 26341-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129621965</v>
       </c>
       <c r="B2" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>129723060</v>
       </c>
       <c r="B3" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>129910129</v>
       </c>
       <c r="B4" t="n">
-        <v>57841</v>
+        <v>57844</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>129917445</v>
       </c>
       <c r="B5" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>129917306</v>
       </c>
       <c r="B6" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>129917397</v>
       </c>
       <c r="B7" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 26341-2025 artfynd.xlsx
+++ b/artfynd/A 26341-2025 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>129723060</v>
       </c>
       <c r="B3" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26341-2025 artfynd.xlsx
+++ b/artfynd/A 26341-2025 artfynd.xlsx
@@ -937,7 +937,7 @@
         <v>129910129</v>
       </c>
       <c r="B4" t="n">
-        <v>57845</v>
+        <v>57930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>129917445</v>
       </c>
       <c r="B5" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>129917306</v>
       </c>
       <c r="B6" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>129917397</v>
       </c>
       <c r="B7" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 26341-2025 artfynd.xlsx
+++ b/artfynd/A 26341-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1446,6 +1446,119 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130349325</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57985</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Paljacka, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>604712</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6978964</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26341-2025 artfynd.xlsx
+++ b/artfynd/A 26341-2025 artfynd.xlsx
@@ -937,7 +937,7 @@
         <v>129910129</v>
       </c>
       <c r="B4" t="n">
-        <v>57930</v>
+        <v>57845</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>129917445</v>
       </c>
       <c r="B5" t="n">
-        <v>57826</v>
+        <v>57741</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>129917306</v>
       </c>
       <c r="B6" t="n">
-        <v>57826</v>
+        <v>57741</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>129917397</v>
       </c>
       <c r="B7" t="n">
-        <v>57826</v>
+        <v>57741</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 26341-2025 artfynd.xlsx
+++ b/artfynd/A 26341-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1559,6 +1559,134 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130611431</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57956</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Paljacka, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>604699</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6978819</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Flög över vägen och satt en stund i träd vid vägkanten.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26341-2025 artfynd.xlsx
+++ b/artfynd/A 26341-2025 artfynd.xlsx
@@ -1451,7 +1451,7 @@
         <v>130349325</v>
       </c>
       <c r="B8" t="n">
-        <v>57985</v>
+        <v>58011</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 26341-2025 artfynd.xlsx
+++ b/artfynd/A 26341-2025 artfynd.xlsx
@@ -1451,7 +1451,7 @@
         <v>130349325</v>
       </c>
       <c r="B8" t="n">
-        <v>58011</v>
+        <v>58013</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>130611431</v>
       </c>
       <c r="B9" t="n">
-        <v>57956</v>
+        <v>57958</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 26341-2025 artfynd.xlsx
+++ b/artfynd/A 26341-2025 artfynd.xlsx
@@ -1451,7 +1451,7 @@
         <v>130349325</v>
       </c>
       <c r="B8" t="n">
-        <v>58013</v>
+        <v>58021</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>130611431</v>
       </c>
       <c r="B9" t="n">
-        <v>57958</v>
+        <v>57966</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 26341-2025 artfynd.xlsx
+++ b/artfynd/A 26341-2025 artfynd.xlsx
@@ -1451,7 +1451,7 @@
         <v>130349325</v>
       </c>
       <c r="B8" t="n">
-        <v>58021</v>
+        <v>58022</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>130611431</v>
       </c>
       <c r="B9" t="n">
-        <v>57966</v>
+        <v>57967</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 26341-2025 artfynd.xlsx
+++ b/artfynd/A 26341-2025 artfynd.xlsx
@@ -1451,7 +1451,7 @@
         <v>130349325</v>
       </c>
       <c r="B8" t="n">
-        <v>58022</v>
+        <v>58023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>130611431</v>
       </c>
       <c r="B9" t="n">
-        <v>57967</v>
+        <v>57968</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 26341-2025 artfynd.xlsx
+++ b/artfynd/A 26341-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129621965</v>
+        <v>129490838</v>
       </c>
       <c r="B2" t="n">
-        <v>57740</v>
+        <v>93235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,43 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -730,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>604761</v>
+        <v>604745</v>
       </c>
       <c r="R2" t="n">
-        <v>6978890</v>
+        <v>6979001</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -760,27 +751,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:51</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:51</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Födosökte på björk</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,6 +765,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -807,10 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129723060</v>
+        <v>129917799</v>
       </c>
       <c r="B3" t="n">
-        <v>57899</v>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -818,21 +795,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -840,32 +817,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Paljacka, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604592</v>
+        <v>604708</v>
       </c>
       <c r="R3" t="n">
-        <v>6979054</v>
+        <v>6979030</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -892,22 +856,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,6 +870,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -934,46 +889,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129910129</v>
+        <v>132177649</v>
       </c>
       <c r="B4" t="n">
-        <v>57930</v>
+        <v>80488</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -981,13 +927,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604663</v>
+        <v>604624</v>
       </c>
       <c r="R4" t="n">
-        <v>6978951</v>
+        <v>6978925</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1011,27 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:26</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:26</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Flög runt mig en liten stund inne i skogen. Strulade med inspelning på telefonen därav dålig bild.</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,6 +971,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1058,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129917445</v>
+        <v>129621965</v>
       </c>
       <c r="B5" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,27 +1028,27 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>födosökande</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Paljacka, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604740</v>
+        <v>604761</v>
       </c>
       <c r="R5" t="n">
-        <v>6978947</v>
+        <v>6978890</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1143,27 +1075,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Sannolikt samma individ som i obsen strax innan.</t>
+          <t>Födosökte på björk</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1193,7 +1125,7 @@
         <v>129917306</v>
       </c>
       <c r="B6" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1320,7 +1252,7 @@
         <v>129917397</v>
       </c>
       <c r="B7" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1448,10 +1380,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130349325</v>
+        <v>129917445</v>
       </c>
       <c r="B8" t="n">
-        <v>58023</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,21 +1391,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1487,7 +1419,11 @@
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1499,10 +1435,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>604712</v>
+        <v>604740</v>
       </c>
       <c r="R8" t="n">
-        <v>6978964</v>
+        <v>6978947</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1529,12 +1465,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Sannolikt samma individ som i obsen strax innan.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1561,27 +1512,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130611431</v>
+        <v>134420318</v>
       </c>
       <c r="B9" t="n">
-        <v>57988</v>
+        <v>57975</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1589,33 +1540,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Paljacka, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>604699</v>
+        <v>604743</v>
       </c>
       <c r="R9" t="n">
-        <v>6978819</v>
+        <v>6978990</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1642,27 +1585,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>09:32</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Flög över vägen och satt en stund i träd vid vägkanten.</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1692,7 +1620,7 @@
         <v>132025443</v>
       </c>
       <c r="B10" t="n">
-        <v>57141</v>
+        <v>57162</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1817,10 +1745,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132177649</v>
+        <v>129723060</v>
       </c>
       <c r="B11" t="n">
-        <v>80434</v>
+        <v>58114</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1828,40 +1756,57 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Paljacka, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>604624</v>
+        <v>604592</v>
       </c>
       <c r="R11" t="n">
-        <v>6978925</v>
+        <v>6979054</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1885,12 +1830,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1899,7 +1854,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1918,52 +1872,64 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132177054</v>
+        <v>130349325</v>
       </c>
       <c r="B12" t="n">
-        <v>99130</v>
+        <v>58114</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Paljacka, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>604653</v>
+        <v>604712</v>
       </c>
       <c r="R12" t="n">
-        <v>6978984</v>
+        <v>6978964</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1987,17 +1953,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Grupp av plantor. Totalt 3 grupper som växte i linje upp mot höjden.</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2006,7 +1967,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2025,52 +1985,72 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132024871</v>
+        <v>129622165</v>
       </c>
       <c r="B13" t="n">
-        <v>99130</v>
+        <v>58057</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Paljacka, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>604657</v>
+        <v>604603</v>
       </c>
       <c r="R13" t="n">
-        <v>6978979</v>
+        <v>6979070</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2094,17 +2074,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>grupp av blommor</t>
+          <t>Kom ifrån söder och fortsatte över myren till skogen på norra sidan tjärnen.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2113,7 +2103,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2132,38 +2121,46 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132176963</v>
+        <v>129910129</v>
       </c>
       <c r="B14" t="n">
-        <v>99130</v>
+        <v>58057</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2171,13 +2168,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>604726</v>
+        <v>604663</v>
       </c>
       <c r="R14" t="n">
-        <v>6978857</v>
+        <v>6978951</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2201,17 +2198,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Grupp av plantor.</t>
+          <t>Flög runt mig en liten stund inne i skogen. Strulade med inspelning på telefonen därav dålig bild.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2220,7 +2227,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2239,52 +2245,64 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132025096</v>
+        <v>130611431</v>
       </c>
       <c r="B15" t="n">
-        <v>99130</v>
+        <v>58057</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Paljacka, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>604654</v>
+        <v>604699</v>
       </c>
       <c r="R15" t="n">
-        <v>6978980</v>
+        <v>6978819</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2308,17 +2326,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>grupp av blommor</t>
+          <t>Flög över vägen och satt en stund i träd vid vägkanten.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2327,7 +2355,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2346,10 +2373,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132867430</v>
+        <v>132024871</v>
       </c>
       <c r="B16" t="n">
-        <v>99132</v>
+        <v>99195</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2385,10 +2412,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>604634</v>
+        <v>604657</v>
       </c>
       <c r="R16" t="n">
-        <v>6978929</v>
+        <v>6978979</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2415,17 +2442,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Grupp av plantor.</t>
+          <t>grupp av blommor</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2450,6 +2477,434 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>132025096</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Paljacka, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>604654</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6978980</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>grupp av blommor</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>132176963</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Paljacka, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>604726</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6978857</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Grupp av plantor.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>132177054</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Paljacka, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>604653</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6978984</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Grupp av plantor. Totalt 3 grupper som växte i linje upp mot höjden.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>132867430</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Paljacka, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>604634</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6978929</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Grupp av plantor.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26341-2025 artfynd.xlsx
+++ b/artfynd/A 26341-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129490838</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129917799</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132177649</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1119,6 +1139,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129621965</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1246,6 +1271,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129917306</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1377,6 +1407,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129917397</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1509,6 +1544,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129917445</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1614,6 +1654,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134420318</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1742,6 +1787,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132025443</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1869,6 +1919,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129723060</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1982,6 +2037,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130349325</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2118,6 +2178,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129622165</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2242,6 +2307,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910129</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2370,6 +2440,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130611431</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2477,6 +2552,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132024871</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2584,6 +2664,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132025096</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2691,6 +2776,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132176963</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2798,6 +2888,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132177054</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2905,8 +3000,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132867430</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>